--- a/hall/resources/sample/VisitorPool.xlsx
+++ b/hall/resources/sample/VisitorPool.xlsx
@@ -28,11 +28,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>掉落id</t>
   </si>
   <si>
+    <t>新手引导抽奖</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
     <t>权重_道具ID_数量</t>
   </si>
   <si>
@@ -45,13 +51,22 @@
     <t>id</t>
   </si>
   <si>
+    <t>NewbieGuideDraw</t>
+  </si>
+  <si>
     <t>detailedDropItem</t>
   </si>
   <si>
     <t>游客</t>
   </si>
   <si>
+    <t>单车骑士</t>
+  </si>
+  <si>
     <t>600_1025101_1|600_1025102_1|600_1025103_1|600_1025104_1|600_1025105_1|600_1025106_1|350_1025301_1|350_1025302_1|350_1025303_1|350_1025304_1|350_1025305_1|350_1025306_1|50_1025501_1|50_1025502_1|50_1025503_1|50_1025504_1|50_1025505_1|50_1025506_1</t>
+  </si>
+  <si>
+    <t>极限玩家</t>
   </si>
   <si>
     <t>550_1025101_1|550_1025102_1|550_1025103_1|550_1025104_1|550_1025105_1|550_1025106_1|300_1025201_1|300_1025202_1|300_1025203_1|300_1025204_1|300_1025205_1|300_1025206_1|100_1025301_1|100_1025302_1|100_1025303_1|100_1025304_1|100_1025305_1|100_1025306_1|40_1025401_1|40_1025402_1|40_1025403_1|40_1025404_1|40_1025405_1|40_1025406_1|15_1025501_1|15_1025502_1|15_1025503_1|15_1025504_1|15_1025505_1|15_1025506_1</t>
@@ -265,6 +280,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -350,12 +371,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -582,7 +597,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -606,16 +621,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -624,42 +639,42 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -706,7 +721,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -714,6 +729,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1247,14 +1265,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:J18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="35.375" customWidth="1"/>
-    <col min="4" max="4" width="16.5" customWidth="1"/>
+    <col min="3" max="3" width="16.125" customWidth="1"/>
+    <col min="4" max="4" width="12.625" customWidth="1"/>
+    <col min="5" max="5" width="35.375" customWidth="1"/>
+    <col min="6" max="6" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:8">
+    <row r="1" ht="16.5" spans="1:10">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1262,69 +1282,97 @@
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:8">
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="2"/>
-    </row>
-    <row r="3" ht="16.5" spans="1:8">
+      <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" ht="16.5" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" ht="16.5" spans="1:8">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" ht="16.5" spans="1:10">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
-    </row>
-    <row r="5" ht="16.5" spans="1:8">
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" ht="16.5" spans="1:10">
       <c r="A5" s="2">
         <v>1001</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" ht="16.5" spans="1:8">
+        <v>9</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1025302</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" ht="16.5" spans="1:10">
       <c r="A6" s="2">
         <v>1002</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" spans="1:8">
-      <c r="E14" s="2"/>
-      <c r="H14" s="3"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="H15" s="4"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="H16" s="4"/>
-    </row>
-    <row r="17" spans="8:8">
-      <c r="H17" s="4"/>
-    </row>
-    <row r="18" spans="8:8">
-      <c r="H18" s="4"/>
+        <v>9</v>
+      </c>
+      <c r="C6" s="3">
+        <v>1025402</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:10">
+      <c r="G14" s="2"/>
+      <c r="J14" s="4"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" spans="10:10">
+      <c r="J17" s="5"/>
+    </row>
+    <row r="18" spans="10:10">
+      <c r="J18" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1346,16 +1394,16 @@
     </row>
     <row r="5" spans="3:11">
       <c r="C5" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="J5" t="str">
         <f>_xlfn.TEXTJOIN("|",TRUE,K7:K43)</f>
@@ -1526,7 +1574,7 @@
     </row>
     <row r="16" spans="3:11">
       <c r="E16" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="3:11">
@@ -1621,7 +1669,7 @@
     </row>
     <row r="23" spans="3:11">
       <c r="E23" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="3:11">
@@ -1758,7 +1806,7 @@
     </row>
     <row r="30" spans="3:11">
       <c r="E30" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="3:11">
@@ -1853,7 +1901,7 @@
     </row>
     <row r="37" spans="3:11">
       <c r="E37" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="3:11">

--- a/hall/resources/sample/VisitorPool.xlsx
+++ b/hall/resources/sample/VisitorPool.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\Manage\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="VisitorPool" sheetId="1" r:id="rId1"/>
@@ -28,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t>掉落id</t>
   </si>
@@ -45,6 +50,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>list&lt;int&gt;{_}</t>
+  </si>
+  <si>
     <t>list&lt;list&lt;int&gt;{_}&gt;{|}</t>
   </si>
   <si>
@@ -64,6 +72,9 @@
   </si>
   <si>
     <t>600_1025101_1|600_1025102_1|600_1025103_1|600_1025104_1|600_1025105_1|600_1025106_1|350_1025301_1|350_1025302_1|350_1025303_1|350_1025304_1|350_1025305_1|350_1025306_1|50_1025501_1|50_1025502_1|50_1025503_1|50_1025504_1|50_1025505_1|50_1025506_1</t>
+  </si>
+  <si>
+    <t>1025402_1803_1804_1805</t>
   </si>
   <si>
     <t>极限玩家</t>
@@ -1268,7 +1279,7 @@
   <dimension ref="A1:J18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="16.125" customWidth="1"/>
+    <col min="3" max="3" width="30.25" customWidth="1"/>
     <col min="4" max="4" width="12.625" customWidth="1"/>
     <col min="5" max="5" width="35.375" customWidth="1"/>
     <col min="6" max="6" width="16.5" customWidth="1"/>
@@ -1295,25 +1306,25 @@
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" s="2"/>
     </row>
     <row r="3" ht="16.5" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:10">
@@ -1328,16 +1339,16 @@
         <v>1001</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" s="2">
         <v>1025302</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" s="2"/>
     </row>
@@ -1346,16 +1357,16 @@
         <v>1002</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="3">
-        <v>1025402</v>
+        <v>10</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:10">
@@ -1394,16 +1405,16 @@
     </row>
     <row r="5" spans="3:11">
       <c r="C5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J5" t="str">
         <f>_xlfn.TEXTJOIN("|",TRUE,K7:K43)</f>
@@ -1574,7 +1585,7 @@
     </row>
     <row r="16" spans="3:11">
       <c r="E16" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="3:11">
@@ -1669,7 +1680,7 @@
     </row>
     <row r="23" spans="3:11">
       <c r="E23" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="3:11">
@@ -1806,7 +1817,7 @@
     </row>
     <row r="30" spans="3:11">
       <c r="E30" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="3:11">
@@ -1901,7 +1912,7 @@
     </row>
     <row r="37" spans="3:11">
       <c r="E37" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="3:11">

--- a/hall/resources/sample/VisitorPool.xlsx
+++ b/hall/resources/sample/VisitorPool.xlsx
@@ -74,7 +74,7 @@
     <t>600_1025101_1|600_1025102_1|600_1025103_1|600_1025104_1|600_1025105_1|600_1025106_1|350_1025301_1|350_1025302_1|350_1025303_1|350_1025304_1|350_1025305_1|350_1025306_1|50_1025501_1|50_1025502_1|50_1025503_1|50_1025504_1|50_1025505_1|50_1025506_1</t>
   </si>
   <si>
-    <t>1025402_1803_1804_1805</t>
+    <t>1025402_1707_1708_1709_1710</t>
   </si>
   <si>
     <t>极限玩家</t>
@@ -1279,7 +1279,7 @@
   <dimension ref="A1:J18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="3" max="3" width="30.25" customWidth="1"/>
+    <col min="3" max="3" width="38.75" customWidth="1"/>
     <col min="4" max="4" width="12.625" customWidth="1"/>
     <col min="5" max="5" width="35.375" customWidth="1"/>
     <col min="6" max="6" width="16.5" customWidth="1"/>
